--- a/users.xlsx
+++ b/users.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,6 +444,16 @@
           <t>phone</t>
         </is>
       </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>username</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>registered_at</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -457,6 +467,33 @@
       <c r="C2" t="inlineStr">
         <is>
           <t>+998917771906</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6501929702</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>𝗶𝗺.𝗗𝗮𝘃𝗿𝗼𝗻</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>+998911443821</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>imdavron1</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2025-10-10T16:25:11.524912</t>
         </is>
       </c>
     </row>
